--- a/output/HS_Code_Summary_Rare_Beauty_8016.xlsx
+++ b/output/HS_Code_Summary_Rare_Beauty_8016.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>USD (na fakturách NEUVEDENA – viz kritické příznaky níže)</t>
+          <t>USD – na všech šesti fakturách uvedeno symbolem $ u jednotkových cen i částek</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -1058,38 +1058,28 @@
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
+          <t>Měna: USD. Na všech šesti fakturách je u jednotkových cen i u částek uveden symbol $ (formát buňky), celková částka faktury je zobrazena např. jako $10 677,40. Pro přepočet použijte celní kurz platný k datu propuštění.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
           <t>Celní hodnota = fakturovaná hodnota položek. Dodací podmínka je DDP Kněževes – při deklaraci je nutné dořešit připočitatelné/odpočitatelné náklady (přeprava a pojištění do místa vstupu do EU) dle čl. 70 a 71 celního kodexu Unie.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>KRITICKÉ PŘÍZNAKY / CRITICAL FLAGS</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>⚠ PREFERENČNÍ VĚTA – NENALEZENA</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>V žádné ze šesti faktur (1383-01 až 1388-01) ani v HBL NENÍ uvedena preferenční věta – prohlášení o preferenčním původu podle Dohody o volném obchodu EU–Korejská republika. Doklady uvádějí pouze '* COUNTRY OF ORIGIN : Made in Korea', což preferenční původ NEPROKAZUJE. Bez preferenční věty nelze uplatnit preferenční sazbu a použije se všeobecná (třetizemní) sazba cla. Pro CN 3304 99 00 je všeobecná sazba cla 0 %, takže dopad na clo je v tomto konkrétním případě nulový (ověřte v TARIC k datu propuštění); DPH se uplatní v plné výši. DOPORUČENÍ: vyžádat od GYC Gayang Corp. doplnění preferenční věty na faktury včetně čísla povolení schváleného vývozce.</t>
         </is>
       </c>
       <c r="B29" s="5" t="n"/>
@@ -1103,27 +1093,27 @@
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="6" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>V žádné ze šesti faktur (1383-01 až 1388-01) ani v HBL NENÍ uvedena preferenční věta – prohlášení o preferenčním původu podle Dohody o volném obchodu EU–Korejská republika. Doklady uvádějí pouze '* COUNTRY OF ORIGIN : Made in Korea', což preferenční původ NEPROKAZUJE. Bez preferenční věty nelze uplatnit preferenční sazbu a použije se všeobecná (třetizemní) sazba cla. Pro CN 3304 99 00 je všeobecná sazba cla 0 %, takže dopad na clo je v tomto konkrétním případě nulový (ověřte v TARIC k datu propuštění); DPH se uplatní v plné výši. DOPORUČENÍ: vyžádat od GYC Gayang Corp. doplnění preferenční věty na faktury včetně čísla povolení schváleného vývozce.</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>CBAM – NEAPLIKUJE SE</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>HS 3304.99 / CN 3304 99 00 (kosmetické přípravky) NENÍ zbožím uvedeným v příloze I nařízení CBAM (cement, elektřina, hnojiva, železo a ocel, hliník, vodík). Vyhledání příjemce v registru reference/CBAM_receivers_CZ.xlsx proto není pro tuto zásilku vyžadováno. Pro úplnost bylo přesto provedeno: příjemce 'Rare Beauty' ani 'Maurice Ward &amp; Co., s.r.o.' se v registru (101 řádků) NENACHÁZÍ – pokud by tato společnost měla někdy dovážet CBAM zboží, je třeba ji do registru doplnit.</t>
         </is>
       </c>
       <c r="B32" s="5" t="n"/>
@@ -1137,27 +1127,27 @@
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="6" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>⚠ MĚNA NENÍ NA FAKTURÁCH UVEDENA</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Všech šest faktur uvádí jednotkové ceny i částky bez označení měny. Vzhledem k tomu, že kupujícím je Rare Beauty Brands Inc. (Boston, USA), je v souhrnu použita měna USD. PŘED PODÁNÍM CELNÍHO PROHLÁŠENÍ POTVRĎTE MĚNU s odesílatelem/klientem a použijte celní kurz platný k datu propuštění.</t>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>HS 3304.99 / CN 3304 99 00 (kosmetické přípravky) NENÍ zbožím uvedeným v příloze I nařízení CBAM (cement, elektřina, hnojiva, železo a ocel, hliník, vodík). Vyhledání příjemce v registru reference/CBAM_receivers_CZ.xlsx proto není pro tuto zásilku vyžadováno. Pro úplnost bylo přesto provedeno: příjemce 'Rare Beauty' ani 'Maurice Ward &amp; Co., s.r.o.' se v registru (101 řádků) NENACHÁZÍ – pokud by tato společnost měla někdy dovážet CBAM zboží, je třeba ji do registru doplnit.</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>⚠ ROZPOR V PLATBĚ PŘEPRAVNÉHO</t>
         </is>
       </c>
       <c r="B35" s="5" t="n"/>
@@ -1171,27 +1161,27 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="6" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>⚠ ROZPOR V PLATBĚ PŘEPRAVNÉHO</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Faktury uvádějí '* FREIGHT COLLECT', HBL KIMXHAM2608001 uvádí 'FREIGHT PREPAID AS ARRANGED'. Rozpor je nutné vyjasnit pro správné stanovení celní hodnoty (připočitatelné náklady dle čl. 71 celního kodexu Unie).</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>POPIS ZBOŽÍ – ZDROJ POUZE ANGLICKY</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
@@ -1205,54 +1195,39 @@
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="6" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>POPIS ZBOŽÍ – ZDROJ POUZE ANGLICKY</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="6" t="n"/>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>V dokladech není k dispozici český popis zboží – faktury uvádějí pouze anglické názvy výrobků. Český popis ve sloupci 'Popis zboží' byl proto sestaven podle nomenklatury CN a názvů výrobků z faktur; původní anglické názvy jsou zachovány v listu 'Detail – položky'.</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="6" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A34:K34"/>
+  <mergeCells count="25">
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="B9:K9"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="B15:K15"/>
     <mergeCell ref="B6:K6"/>
+    <mergeCell ref="A36:K36"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A41:K41"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B16:K16"/>
-    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A33:K33"/>
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="B11:K11"/>
@@ -1263,10 +1238,7 @@
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="B13:K13"/>
     <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A28:K28"/>
     <mergeCell ref="B10:K10"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
